--- a/reports/meta_intel_2026-W23.xlsx
+++ b/reports/meta_intel_2026-W23.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-01 14:06 UTC</t>
+          <t>Generated: 2026-06-01 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1460,36 +1460,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>969531769204739</t>
+          <t>1868277354563662</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>199</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1500,36 +1500,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1325634685561342</t>
+          <t>1362684515702149</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1868277354563662</t>
+          <t>1938930663325095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1362684515702149</t>
+          <t>1852060685669387</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1605,11 +1605,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1938930663325095</t>
+          <t>966816482430409</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1645,11 +1645,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1852060685669387</t>
+          <t>1588345672369492</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1685,11 +1685,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>966816482430409</t>
+          <t>841302105060560</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1588345672369492</t>
+          <t>1296748252140081</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1765,11 +1765,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>841302105060560</t>
+          <t>3976129939359406</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1296748252140081</t>
+          <t>1177236264536592</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3976129939359406</t>
+          <t>4072587919646468</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1885,11 +1885,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>206</v>
+        <v>50</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1177236264536592</t>
+          <t>1943193019573119</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1925,11 +1925,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4072587919646468</t>
+          <t>2260190851070799</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1965,11 +1965,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>199</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1943193019573119</t>
+          <t>1630159098158899</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1995,21 +1995,21 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2260190851070799</t>
+          <t>796404973298946</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1630159098158899</t>
+          <t>3888948801242426</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2075,21 +2075,21 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>796404973298946</t>
+          <t>3727759467519562</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2125,11 +2125,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3888948801242426</t>
+          <t>850477457839087</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2155,21 +2155,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach Oma &amp; Opa glücklich!🫶 ➡️ Jetzt 120€ sparen! (Gilt nur für kurze Zeit) Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>39</v>
+        <v>161</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2185,7 +2190,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3727759467519562</t>
+          <t>1549478262721918</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2205,11 +2210,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2225,7 +2230,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>850477457839087</t>
+          <t>2040130603507445</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2235,17 +2240,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mach Oma &amp; Opa glücklich!🫶 ➡️ Jetzt 120€ sparen! (Gilt nur für kurze Zeit) Sorry, we're having trouble playing this video.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1549478262721918</t>
+          <t>1171548231746967</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2290,11 +2290,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2040130603507445</t>
+          <t>871339118687590</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2330,11 +2330,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1171548231746967</t>
+          <t>2761672647588250</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2370,11 +2370,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>198</v>
+        <v>110</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>871339118687590</t>
+          <t>1893837991150333</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2400,21 +2400,21 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Jetzt enna 30 Tage kostenlos testen! 🎁 Videocalls, Lieblingssendungen oder digitaler Terminkalender: enna holt die schönen Seiten moderner Technik ins Wohnzimmer deiner Großeltern – ganz ohne Technikstress. ✨ Was enna möglich macht:</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>✅ Digitale Fotoalben für gemeinsame Momente</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2761672647588250</t>
+          <t>1196762821852142</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2440,21 +2440,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>⭐️ 4,7 Sterne Bewertung</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Learn More</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2470,7 +2475,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1893837991150333</t>
+          <t>2393916927736067</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2480,21 +2485,21 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Jetzt enna 30 Tage kostenlos testen! 🎁 Videocalls, Lieblingssendungen oder digitaler Terminkalender: enna holt die schönen Seiten moderner Technik ins Wohnzimmer deiner Großeltern – ganz ohne Technikstress. ✨ Was enna möglich macht:</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅ Digitale Fotoalben für gemeinsame Momente</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2510,7 +2515,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1196762821852142</t>
+          <t>1373162224393589</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2520,26 +2525,21 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>⭐️ 4,7 Sterne Bewertung</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Learn More</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2393916927736067</t>
+          <t>804595359053733</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2575,11 +2575,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1373162224393589</t>
+          <t>2457105498055853</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2605,21 +2605,21 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Jetzt enna 30 Tage kostenlos testen! 🎁 Videocalls, Lieblingssendungen oder digitaler Terminkalender: enna holt die schönen Seiten moderner Technik ins Wohnzimmer deiner Großeltern – ganz ohne Technikstress. ✨ Was enna möglich macht:</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>✅ Digitale Fotoalben für gemeinsame Momente</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>206</v>
+        <v>42</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>804595359053733</t>
+          <t>25607802815471461</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2670,36 +2670,36 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2457105498055853</t>
+          <t>1604340910795794</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Jetzt enna 30 Tage kostenlos testen! 🎁 Videocalls, Lieblingssendungen oder digitaler Terminkalender: enna holt die schönen Seiten moderner Technik ins Wohnzimmer deiner Großeltern – ganz ohne Technikstress. ✨ Was enna möglich macht:</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ Digitale Fotoalben für gemeinsame Momente</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2710,36 +2710,41 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>25607802815471461</t>
+          <t>1510732740710867</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Preserve their stories, and their voice, in a book that lasts generations. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1604340910795794</t>
+          <t>1652739722437976</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2770,16 +2775,16 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2795,7 +2800,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1510732740710867</t>
+          <t>2460360471077841</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2805,7 +2810,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Preserve their stories, and their voice, in a book that lasts generations. Sorry, we're having trouble playing this video.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2840,7 +2845,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1652739722437976</t>
+          <t>1907813709863061</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2850,21 +2855,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Turn memories into a lasting keepsake</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2880,7 +2885,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2460360471077841</t>
+          <t>986777303695569</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2890,26 +2895,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1907813709863061</t>
+          <t>830570699644006</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2945,11 +2945,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>986777303695569</t>
+          <t>977072525149646</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2975,21 +2975,26 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>830570699644006</t>
+          <t>943864791615557</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3015,12 +3020,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Turn memories into a lasting keepsake</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3045,7 +3050,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>977072525149646</t>
+          <t>792414230413551</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3055,26 +3060,21 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>The Only Book That Let's You Listen to Their Story.</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>943864791615557</t>
+          <t>4209711686009806</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>792414230413551</t>
+          <t>1680810166448399</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3145,16 +3145,16 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4209711686009806</t>
+          <t>1107552519108914</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1680810166448399</t>
+          <t>1521599959561340</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3225,16 +3225,16 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Her Story. Bound Forever.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1107552519108914</t>
+          <t>1009981694791489</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1521599959561340</t>
+          <t>984361874565809</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3300,21 +3300,21 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Turn memories into a lasting keepsake</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1009981694791489</t>
+          <t>1613608029697579</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3345,16 +3345,16 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3365,36 +3365,41 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>984361874565809</t>
+          <t>1685628942752739</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Turn memories into a lasting keepsake</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3405,36 +3410,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1613608029697579</t>
+          <t>1657931948555000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3450,7 +3455,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1685628942752739</t>
+          <t>1688004719222897</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3475,11 +3480,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3495,7 +3500,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1657931948555000</t>
+          <t>1643835923556092</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3505,21 +3510,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3535,7 +3545,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1688004719222897</t>
+          <t>2082672142583809</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3545,7 +3555,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3560,11 +3570,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3580,7 +3590,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1643835923556092</t>
+          <t>952068907735194</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3605,11 +3615,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3625,7 +3635,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2082672142583809</t>
+          <t>838679825886616</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3635,26 +3645,21 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3670,7 +3675,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>952068907735194</t>
+          <t>944975184903429</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3695,11 +3700,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>838679825886616</t>
+          <t>1948413482455351</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3725,21 +3730,21 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>It’s helping them continue to thrive there ✨</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3755,7 +3760,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>944975184903429</t>
+          <t>3024152471117079</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3765,7 +3770,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>A digital care companion designed for healthy, happy aging at home. Get it free today by your local Area Agency on Aging or your Medicaid provider. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3780,11 +3785,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1948413482455351</t>
+          <t>26794090103575688</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3820,11 +3825,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3840,7 +3845,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3024152471117079</t>
+          <t>2383639082136267</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3850,26 +3855,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A digital care companion designed for healthy, happy aging at home. Get it free today by your local Area Agency on Aging or your Medicaid provider. Sorry, we're having trouble playing this video.</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26794090103575688</t>
+          <t>2052874168989707</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3895,21 +3895,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
+          <t>A digital care companion designed for healthy, happy aging at home. Get it at no cost today by the Area Agency on Aging of Broward County. Check you eligibility today at ElliQ.com/free Apply for a free ElliQ today!</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>It’s helping them continue to thrive there ✨</t>
+          <t>Get it free today</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2383639082136267</t>
+          <t>1773179040333547</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3945,11 +3945,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2052874168989707</t>
+          <t>1682907829804633</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3975,108 +3975,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A digital care companion designed for healthy, happy aging at home. Get it at no cost today by the Area Agency on Aging of Broward County. Check you eligibility today at ElliQ.com/free Apply for a free ElliQ today!</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Get it free today</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="J81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1773179040333547</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>✨ A friendly voice</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>39</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1682907829804633</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ElliQ</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>27</v>
-      </c>
-      <c r="J83" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4093,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -4110,7 +4030,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-01 14:06 UTC</t>
+          <t>Generated: 2026-06-01 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4049,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -4160,187 +4080,173 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1325634685561342</t>
+          <t>1550643250123045</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1550643250123045</t>
+          <t>1553640199509767</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1553640199509767</t>
+          <t>1653680055692542</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1653680055692542</t>
+          <t>1658428992119996</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1658428992119996</t>
+          <t>1775246913443819</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1775246913443819</t>
+          <t>1874079009932508</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1874079009932508</t>
+          <t>1893837991150333</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1893837991150333</t>
+          <t>1948413482455351</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1948413482455351</t>
+          <t>2050751649119006</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2050751649119006</t>
+          <t>2383639082136267</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2383639082136267</t>
+          <t>2457105498055853</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2457105498055853</t>
+          <t>25607802815471461</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25607802815471461</t>
+          <t>26677419218566558</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26677419218566558</t>
+          <t>26794090103575688</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26794090103575688</t>
+          <t>26955183910799087</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26955183910799087</t>
+          <t>27187697080826605</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27187697080826605</t>
+          <t>3024152471117079</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3024152471117079</t>
+          <t>3736725189799420</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3736725189799420</t>
+          <t>4084111768387600</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4084111768387600</t>
+          <t>838679825886616</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>838679825886616</t>
+          <t>865242469956705</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>865242469956705</t>
+          <t>908374725587319</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>908374725587319</t>
+          <t>966868629514782</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>966868629514782</t>
+          <t>971539412358822</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
-        <is>
-          <t>969531769204739</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>971539412358822</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
         <is>
           <t>979857914909399</t>
         </is>
